--- a/docs/新規採用時研修_虐待防止.xlsx
+++ b/docs/新規採用時研修_虐待防止.xlsx
@@ -956,7 +956,7 @@
     <row r="56" ht="18.75" customHeight="1">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>受講記録（様式5「新規採用時研修記録」の項目2に転記）</t>
+          <t>受講記録（様式5「新規採用時研修記録」に転記）</t>
         </is>
       </c>
     </row>
